--- a/downloads/planilha-codificacao.xlsx
+++ b/downloads/planilha-codificacao.xlsx
@@ -450,7 +450,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Professor</t>
+          <t>Entrevistado</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
